--- a/ABB_Biennial_Visual_Check.xlsx
+++ b/ABB_Biennial_Visual_Check.xlsx
@@ -105,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -119,11 +119,74 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -171,6 +234,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -245,6 +317,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="828675" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="828675" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -559,6 +691,10 @@
           <t>1.  IED AND SITE INFORMATION</t>
         </is>
       </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="18" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -571,6 +707,9 @@
           <t>REG670  /  RET670  (circle one)</t>
         </is>
       </c>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="18" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -579,6 +718,9 @@
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -587,6 +729,9 @@
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -595,6 +740,9 @@
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -603,6 +751,9 @@
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -611,6 +762,9 @@
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -619,6 +773,9 @@
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -627,6 +784,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -639,6 +799,9 @@
           <t>(2 years from date above)</t>
         </is>
       </c>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="18" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -646,6 +809,10 @@
           <t>2.  CONNECTION METHOD</t>
         </is>
       </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="18" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -655,6 +822,10 @@
 OPTION C — Ethernet + web browser: Navigate to IED IP address in browser (if web server enabled).</t>
         </is>
       </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -667,6 +838,9 @@
           <t>LHMI only  /  Ethernet + PCM600  /  Ethernet + browser  (delete as applicable)</t>
         </is>
       </c>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="18" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -674,6 +848,10 @@
           <t>3.  SELF-TEST AND IED STATUS  (INTERRSIG self-supervision)</t>
         </is>
       </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -681,6 +859,10 @@
           <t>LHMI path: Main menu → Diagnostics → IED status → Signals → INTERRSIG.  All signals should show NORMAL (0). A FAIL signal asserts the INTERNAL FAIL contact on the PSM. Hardware modules: Main menu → Diagnostics → Hardware → Module status.</t>
         </is>
       </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -924,6 +1106,10 @@
           <t>4.  ANALOGUE MEASUREMENTS  (Primary Values)</t>
         </is>
       </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="18" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -931,6 +1117,10 @@
           <t>LHMI: Main menu → Measurements → [function block, e.g. T2WPDIF, GENPDIF, OC4PTOC] → monitored data.  All values displayed in primary units. Record current load values below.  PCM600: Signal Monitor shows live primary values.</t>
         </is>
       </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="18" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -1148,6 +1338,10 @@
           <t>5.  CLOCK AND TIME SYNCHRONISATION</t>
         </is>
       </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="18" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -1259,6 +1453,10 @@
           <t>6.  RECENT EVENTS  (record most recent disturbance records / events)</t>
         </is>
       </c>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="18" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -1266,6 +1464,10 @@
           <t>LHMI: Main menu → Events → Disturbance records list (most recent first).  PCM600: Event viewer shows all logged events with timestamps.  Record the most recent events; flag any unexplained trips or alarms.</t>
         </is>
       </c>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="18" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -1289,6 +1491,7 @@
           <t>Event Description / Type</t>
         </is>
       </c>
+      <c r="E56" s="18" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
@@ -1297,6 +1500,7 @@
       <c r="B57" s="4" t="n"/>
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
+      <c r="E57" s="18" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n">
@@ -1305,6 +1509,7 @@
       <c r="B58" s="13" t="n"/>
       <c r="C58" s="13" t="n"/>
       <c r="D58" s="13" t="n"/>
+      <c r="E58" s="18" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
@@ -1313,6 +1518,7 @@
       <c r="B59" s="4" t="n"/>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
+      <c r="E59" s="18" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n">
@@ -1321,6 +1527,7 @@
       <c r="B60" s="13" t="n"/>
       <c r="C60" s="13" t="n"/>
       <c r="D60" s="13" t="n"/>
+      <c r="E60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
@@ -1329,6 +1536,7 @@
       <c r="B61" s="4" t="n"/>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
+      <c r="E61" s="18" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n">
@@ -1337,6 +1545,7 @@
       <c r="B62" s="13" t="n"/>
       <c r="C62" s="13" t="n"/>
       <c r="D62" s="13" t="n"/>
+      <c r="E62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
@@ -1345,6 +1554,7 @@
       <c r="B63" s="4" t="n"/>
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
+      <c r="E63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n">
@@ -1353,6 +1563,7 @@
       <c r="B64" s="13" t="n"/>
       <c r="C64" s="13" t="n"/>
       <c r="D64" s="13" t="n"/>
+      <c r="E64" s="18" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
@@ -1361,6 +1572,7 @@
       <c r="B65" s="4" t="n"/>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
+      <c r="E65" s="18" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n">
@@ -1369,6 +1581,7 @@
       <c r="B66" s="13" t="n"/>
       <c r="C66" s="13" t="n"/>
       <c r="D66" s="13" t="n"/>
+      <c r="E66" s="18" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
@@ -1377,6 +1590,7 @@
       <c r="B67" s="4" t="n"/>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
+      <c r="E67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n">
@@ -1385,6 +1599,7 @@
       <c r="B68" s="13" t="n"/>
       <c r="C68" s="13" t="n"/>
       <c r="D68" s="13" t="n"/>
+      <c r="E68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1393,6 +1608,9 @@
         </is>
       </c>
       <c r="B69" s="4" t="n"/>
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="18" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -1400,6 +1618,10 @@
           <t>7.  DCS / ABB 800XA COMMUNICATION CHECK</t>
         </is>
       </c>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="18" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -1407,6 +1629,10 @@
           <t>Open the IED faceplate in the ABB 800XA control system. Verify live values (currents, IED status indicators) are updating. The 800XA communicates via IEC 61850 GOOSE / MMS. No yellow or red communication alarm objects should be present.</t>
         </is>
       </c>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="17" t="n"/>
+      <c r="E72" s="18" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
@@ -1430,6 +1656,7 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="E73" s="18" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -1444,6 +1671,7 @@
       </c>
       <c r="C74" s="10" t="n"/>
       <c r="D74" s="4" t="n"/>
+      <c r="E74" s="18" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1458,6 +1686,7 @@
       </c>
       <c r="C75" s="10" t="n"/>
       <c r="D75" s="4" t="n"/>
+      <c r="E75" s="18" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -1472,6 +1701,7 @@
       </c>
       <c r="C76" s="10" t="n"/>
       <c r="D76" s="4" t="n"/>
+      <c r="E76" s="18" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -1486,6 +1716,7 @@
       </c>
       <c r="C77" s="10" t="n"/>
       <c r="D77" s="4" t="n"/>
+      <c r="E77" s="18" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -1500,6 +1731,7 @@
       </c>
       <c r="C78" s="10" t="n"/>
       <c r="D78" s="4" t="n"/>
+      <c r="E78" s="18" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -1507,6 +1739,10 @@
           <t>8.  OPTIONAL — CLEAR EVENT BUFFERS  (only if required by your procedure)</t>
         </is>
       </c>
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="17" t="n"/>
+      <c r="D80" s="17" t="n"/>
+      <c r="E80" s="18" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="14" t="inlineStr">
@@ -1514,6 +1750,10 @@
           <t>Only clear events if required by site procedure. Ensure all events have been downloaded/recorded BEFORE clearing. LHMI: Main menu → Events → [select event] → Clear  (or Clear all).  Internal events (INTERRSIG log) clear automatically after 40 events (FIFO).</t>
         </is>
       </c>
+      <c r="B81" s="17" t="n"/>
+      <c r="C81" s="17" t="n"/>
+      <c r="D81" s="17" t="n"/>
+      <c r="E81" s="18" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
@@ -1537,6 +1777,7 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="E82" s="18" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1551,6 +1792,7 @@
       </c>
       <c r="C83" s="10" t="n"/>
       <c r="D83" s="4" t="n"/>
+      <c r="E83" s="18" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -1565,6 +1807,7 @@
       </c>
       <c r="C84" s="10" t="n"/>
       <c r="D84" s="4" t="n"/>
+      <c r="E84" s="18" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -1572,30 +1815,32 @@
           <t>9.  OBSERVATIONS AND CORRECTIVE ACTIONS</t>
         </is>
       </c>
+      <c r="B86" s="17" t="n"/>
+      <c r="C86" s="17" t="n"/>
+      <c r="D86" s="17" t="n"/>
+      <c r="E86" s="18" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="15" t="n"/>
+      <c r="B87" s="19" t="n"/>
+      <c r="C87" s="19" t="n"/>
+      <c r="D87" s="19" t="n"/>
+      <c r="E87" s="20" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="16" t="n"/>
-      <c r="B88" s="16" t="n"/>
-      <c r="C88" s="16" t="n"/>
-      <c r="D88" s="16" t="n"/>
-      <c r="E88" s="16" t="n"/>
+      <c r="A88" s="21" t="n"/>
+      <c r="E88" s="22" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="16" t="n"/>
-      <c r="B89" s="16" t="n"/>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="16" t="n"/>
-      <c r="E89" s="16" t="n"/>
+      <c r="A89" s="21" t="n"/>
+      <c r="E89" s="22" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="16" t="n"/>
-      <c r="B90" s="16" t="n"/>
-      <c r="C90" s="16" t="n"/>
-      <c r="D90" s="16" t="n"/>
-      <c r="E90" s="16" t="n"/>
+      <c r="A90" s="23" t="n"/>
+      <c r="B90" s="24" t="n"/>
+      <c r="C90" s="24" t="n"/>
+      <c r="D90" s="24" t="n"/>
+      <c r="E90" s="25" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -1603,6 +1848,10 @@
           <t>10.  SIGN-OFF</t>
         </is>
       </c>
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="18" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
@@ -1625,6 +1874,7 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="E93" s="18" t="n"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
@@ -1635,6 +1885,7 @@
       <c r="B94" s="4" t="n"/>
       <c r="C94" s="4" t="n"/>
       <c r="D94" s="4" t="n"/>
+      <c r="E94" s="18" t="n"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
@@ -1645,12 +1896,13 @@
       <c r="B95" s="4" t="n"/>
       <c r="C95" s="4" t="n"/>
       <c r="D95" s="4" t="n"/>
+      <c r="E95" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="54">
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="D60:E60"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="D60:E60"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="D63:E63"/>
     <mergeCell ref="B6:E6"/>
@@ -1705,6 +1957,15 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1737,6 +1998,10 @@
           <t>1.  IED AND SITE INFORMATION</t>
         </is>
       </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="18" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1749,6 +2014,9 @@
           <t>REF615  /  RET615  /  REM615  /  REU615  (circle one)</t>
         </is>
       </c>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="18" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1757,6 +2025,9 @@
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1765,6 +2036,9 @@
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1773,6 +2047,9 @@
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1781,6 +2058,9 @@
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1789,6 +2069,9 @@
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1797,6 +2080,9 @@
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1805,6 +2091,9 @@
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1817,6 +2106,9 @@
           <t>(2 years from date above)</t>
         </is>
       </c>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="18" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1824,6 +2116,10 @@
           <t>2.  CONNECTION METHOD</t>
         </is>
       </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="18" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1833,6 +2129,10 @@
 OPTION C — Ethernet + web browser: Newer 615 C/D models support a built-in web server — navigate to IED IP address in a browser.</t>
         </is>
       </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1845,6 +2145,9 @@
           <t>LHMI only  /  Ethernet + PCM600  /  Ethernet + browser  (delete as applicable)</t>
         </is>
       </c>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="18" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1852,6 +2155,10 @@
           <t>3.  SELF-TEST AND IED STATUS</t>
         </is>
       </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1859,6 +2166,10 @@
           <t>Key LED indicators on front panel:  READY (green, solid) = IED healthy and in service.  START (yellow) = protection element picked up (may be normal under load).  TRIP (red) = protection has tripped.  Self-supervision: LHMI: Main menu → Monitoring → Self-supervision → IED status.</t>
         </is>
       </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -2026,6 +2337,10 @@
           <t>4.  ANALOGUE MEASUREMENTS  (Primary Values)</t>
         </is>
       </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="18" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -2033,6 +2348,10 @@
           <t>LHMI: Main menu → Monitoring → Measurements → Current (or Voltage).  All values shown in primary units. PCM600 Signal Monitor also displays live primary values.  Record current values. Flag anything obviously abnormal (e.g. one phase zero while others are loaded).</t>
         </is>
       </c>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="18" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -2221,6 +2540,10 @@
           <t>5.  CLOCK AND TIME SYNCHRONISATION</t>
         </is>
       </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="18" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -2313,6 +2636,10 @@
           <t>6.  RECENT EVENTS  (record most recent events from the event list)</t>
         </is>
       </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="18" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2320,6 +2647,10 @@
           <t>LHMI: Main menu → Events → Event list (most recent first).  PCM600: Event viewer.  Record the most recent events. Flag any unexplained TRIP or FAULT events.</t>
         </is>
       </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="18" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -2343,6 +2674,7 @@
           <t>Event Description / Type</t>
         </is>
       </c>
+      <c r="E49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">
@@ -2351,6 +2683,7 @@
       <c r="B50" s="4" t="n"/>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
+      <c r="E50" s="18" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n">
@@ -2359,6 +2692,7 @@
       <c r="B51" s="13" t="n"/>
       <c r="C51" s="13" t="n"/>
       <c r="D51" s="13" t="n"/>
+      <c r="E51" s="18" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
@@ -2367,6 +2701,7 @@
       <c r="B52" s="4" t="n"/>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
+      <c r="E52" s="18" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n">
@@ -2375,6 +2710,7 @@
       <c r="B53" s="13" t="n"/>
       <c r="C53" s="13" t="n"/>
       <c r="D53" s="13" t="n"/>
+      <c r="E53" s="18" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -2383,6 +2719,7 @@
       <c r="B54" s="4" t="n"/>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
+      <c r="E54" s="18" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="n">
@@ -2391,6 +2728,7 @@
       <c r="B55" s="13" t="n"/>
       <c r="C55" s="13" t="n"/>
       <c r="D55" s="13" t="n"/>
+      <c r="E55" s="18" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
@@ -2399,6 +2737,7 @@
       <c r="B56" s="4" t="n"/>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
+      <c r="E56" s="18" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="n">
@@ -2407,6 +2746,7 @@
       <c r="B57" s="13" t="n"/>
       <c r="C57" s="13" t="n"/>
       <c r="D57" s="13" t="n"/>
+      <c r="E57" s="18" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -2415,6 +2755,7 @@
       <c r="B58" s="4" t="n"/>
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
+      <c r="E58" s="18" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n">
@@ -2423,6 +2764,7 @@
       <c r="B59" s="13" t="n"/>
       <c r="C59" s="13" t="n"/>
       <c r="D59" s="13" t="n"/>
+      <c r="E59" s="18" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
@@ -2431,6 +2773,7 @@
       <c r="B60" s="4" t="n"/>
       <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
+      <c r="E60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n">
@@ -2439,6 +2782,7 @@
       <c r="B61" s="13" t="n"/>
       <c r="C61" s="13" t="n"/>
       <c r="D61" s="13" t="n"/>
+      <c r="E61" s="18" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2447,6 +2791,9 @@
         </is>
       </c>
       <c r="B62" s="4" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="18" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -2454,6 +2801,10 @@
           <t>7.  DCS / ABB 800XA COMMUNICATION CHECK</t>
         </is>
       </c>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="18" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -2461,6 +2812,10 @@
           <t>Open the IED faceplate in the ABB 800XA control system. Verify live values and IED status are updating. The 615 series typically communicates via IEC 61850, DNP3.0, or Modbus.  No yellow or red communication alarm objects should be present on the 800XA faceplate.</t>
         </is>
       </c>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="18" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -2484,6 +2839,7 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="E66" s="18" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2498,6 +2854,7 @@
       </c>
       <c r="C67" s="10" t="n"/>
       <c r="D67" s="4" t="n"/>
+      <c r="E67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2512,6 +2869,7 @@
       </c>
       <c r="C68" s="10" t="n"/>
       <c r="D68" s="4" t="n"/>
+      <c r="E68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2526,6 +2884,7 @@
       </c>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="4" t="n"/>
+      <c r="E69" s="18" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2540,6 +2899,7 @@
       </c>
       <c r="C70" s="10" t="n"/>
       <c r="D70" s="4" t="n"/>
+      <c r="E70" s="18" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2554,6 +2914,7 @@
       </c>
       <c r="C71" s="10" t="n"/>
       <c r="D71" s="4" t="n"/>
+      <c r="E71" s="18" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -2561,6 +2922,10 @@
           <t>8.  OPTIONAL — CLEAR EVENTS  (only if required by your procedure)</t>
         </is>
       </c>
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="17" t="n"/>
+      <c r="E73" s="18" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
@@ -2568,6 +2933,10 @@
           <t>Only clear events if required by site procedure. Download/record all events BEFORE clearing. LHMI: Main menu → Events → Event list → Clear all (or select individual events).</t>
         </is>
       </c>
+      <c r="B74" s="17" t="n"/>
+      <c r="C74" s="17" t="n"/>
+      <c r="D74" s="17" t="n"/>
+      <c r="E74" s="18" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
@@ -2591,6 +2960,7 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="E75" s="18" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2605,6 +2975,7 @@
       </c>
       <c r="C76" s="10" t="n"/>
       <c r="D76" s="4" t="n"/>
+      <c r="E76" s="18" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2619,6 +2990,7 @@
       </c>
       <c r="C77" s="10" t="n"/>
       <c r="D77" s="4" t="n"/>
+      <c r="E77" s="18" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -2626,30 +2998,32 @@
           <t>9.  OBSERVATIONS AND CORRECTIVE ACTIONS</t>
         </is>
       </c>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="17" t="n"/>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="18" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="15" t="n"/>
+      <c r="B80" s="19" t="n"/>
+      <c r="C80" s="19" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="20" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="16" t="n"/>
-      <c r="B81" s="16" t="n"/>
-      <c r="C81" s="16" t="n"/>
-      <c r="D81" s="16" t="n"/>
-      <c r="E81" s="16" t="n"/>
+      <c r="A81" s="21" t="n"/>
+      <c r="E81" s="22" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="16" t="n"/>
-      <c r="B82" s="16" t="n"/>
-      <c r="C82" s="16" t="n"/>
-      <c r="D82" s="16" t="n"/>
-      <c r="E82" s="16" t="n"/>
+      <c r="A82" s="21" t="n"/>
+      <c r="E82" s="22" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="16" t="n"/>
-      <c r="B83" s="16" t="n"/>
-      <c r="C83" s="16" t="n"/>
-      <c r="D83" s="16" t="n"/>
-      <c r="E83" s="16" t="n"/>
+      <c r="A83" s="23" t="n"/>
+      <c r="B83" s="24" t="n"/>
+      <c r="C83" s="24" t="n"/>
+      <c r="D83" s="24" t="n"/>
+      <c r="E83" s="25" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -2657,6 +3031,10 @@
           <t>10.  SIGN-OFF</t>
         </is>
       </c>
+      <c r="B85" s="17" t="n"/>
+      <c r="C85" s="17" t="n"/>
+      <c r="D85" s="17" t="n"/>
+      <c r="E85" s="18" t="n"/>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -2679,6 +3057,7 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="E86" s="18" t="n"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -2689,6 +3068,7 @@
       <c r="B87" s="4" t="n"/>
       <c r="C87" s="4" t="n"/>
       <c r="D87" s="4" t="n"/>
+      <c r="E87" s="18" t="n"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
@@ -2699,13 +3079,14 @@
       <c r="B88" s="4" t="n"/>
       <c r="C88" s="4" t="n"/>
       <c r="D88" s="4" t="n"/>
+      <c r="E88" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="54">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D60:E60"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="D60:E60"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A15:E15"/>
@@ -2759,5 +3140,14 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ABB_Biennial_Visual_Check.xlsx
+++ b/ABB_Biennial_Visual_Check.xlsx
@@ -4,67 +4,119 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="670 Check Sheet" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="615 Check Sheet" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000000FF"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
       <i val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -76,32 +128,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E7"/>
+        <fgColor rgb="FFFFF8E7"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,6 +176,7 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -183,59 +242,137 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="53">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,77 +380,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9E2F3"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFF8E7"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF1F4E79"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -380,41 +525,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -422,1544 +567,1467 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E99"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" style="22" min="1" max="1"/>
+    <col width="34" customWidth="1" style="22" min="2" max="2"/>
+    <col width="14.94" customWidth="1" style="22" min="3" max="3"/>
+    <col width="12" customWidth="1" style="22" min="4" max="4"/>
+    <col width="10.91" customWidth="1" style="22" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="27.75" customHeight="1" s="23">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>ABB RELION 670 IED — BIENNIAL (2-YEARLY) VISUAL CHECK SHEET  (REG670 / RET670)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="2" ht="26.1" customHeight="1" s="23"/>
+    <row r="3" ht="18" customHeight="1" s="23">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>1.  IED AND SITE INFORMATION</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="17" t="n"/>
-      <c r="E3" s="18" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="27" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="23">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>IED Model</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>REG670  /  RET670  (circle one)</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="18" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="27" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="23">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Protected Equipment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="18" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="27" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="23">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Site / Substation</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="18" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="27" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="23">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>IED Name (Station / Bay)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="18" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="27" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="23">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Panel / Cubicle Tag</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="27" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="23">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Work Order No.</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="18" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="23">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Date of Check</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="18" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="27" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="23">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Technician Name</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="18" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="27" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="23">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Next Check Due</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>(2 years from date above)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="18" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="27" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="23">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>2.  CONNECTION METHOD</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="27" t="n"/>
+    </row>
+    <row r="15" ht="60" customHeight="1" s="23">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>OPTION A — LHMI only (no laptop): The RET/REG670 has a full graphical touchscreen or keypad LHMI. Navigate with arrow keys / touchscreen. Main menu accessible from the LHMI home screen.
 OPTION B — Ethernet + PCM600 laptop: Connect laptop Ethernet to IED front port (RJ45). Open PCM600 → Online &gt; Signal Monitor for live values. IP address from LHMI: Main menu → Settings → Communication → Ethernet.
 OPTION C — Ethernet + web browser: Navigate to IED IP address in browser (if web server enabled).</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="18" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="27" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="23">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Connection method used today</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>LHMI only  /  Ethernet + PCM600  /  Ethernet + browser  (delete as applicable)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="18" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="27" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="23">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>3.  SELF-TEST AND IED STATUS  (INTERRSIG self-supervision)</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="18" t="n"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="27" t="n"/>
+    </row>
+    <row r="19" ht="39.75" customHeight="1" s="23">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>LHMI path: Main menu → Diagnostics → IED status → Signals → INTERRSIG.  All signals should show NORMAL (0). A FAIL signal asserts the INTERNAL FAIL contact on the PSM. Hardware modules: Main menu → Diagnostics → Hardware → Module status.</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="27" t="n"/>
+    </row>
+    <row r="20" ht="27.75" customHeight="1" s="23">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Check Item</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>LHMI Path / How to Read</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="23">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Normal LED (green, fixed)</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Visual — front panel upper-left LED</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Green, solid</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="29" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="23">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>No alarm LEDs active</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Visual — front panel LED indicators (15 programmable LEDs)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>All off (or known/accepted)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="29" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>INTERRSIG — FAIL signal</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Diagnostics → IED status → Signals</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>NORMAL (0)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="23">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>INTERRSIG — WARNING signal</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Same path as above</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>NORMAL (0)</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="29" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="23">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>INTERRSIG — RTCERROR (clock error)</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Same path as above</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>NORMAL (0)</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="23">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>INTERRSIG — TIMESYNCHERROR</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Same path as above</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>NORMAL (0)</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="29" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="23">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>INTERRSIG — WATCHDOG</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Same path as above</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>NORMAL (0)</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="29" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="23">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>INTERNAL FAIL contact (PSM terminal)</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Measure across PSM INTERNAL FAIL output terminals</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>Contact OPEN (IED healthy)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="29" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="23">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>PSM module status</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Diagnostics → Hardware</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="29" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="23">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>BIM / BOM / TRM module status</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Diagnostics → Hardware</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="29" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="23">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Internal events — any recent FAILs?</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Diagnostics → IED status → Internal events</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>No unexplained FAIL events</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="4" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="D31" s="35" t="n"/>
+      <c r="E31" s="29" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="23">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>4.  ANALOGUE MEASUREMENTS  (Primary Values)</t>
         </is>
       </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="18" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="27" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="23">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Measurements → [function block, e.g. T2WPDIF, GENPDIF, OC4PTOC] → monitored data.  All values displayed in primary units. Record current load values below.  PCM600: Signal Monitor shows live primary values.</t>
         </is>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="17" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="18" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="27" t="n"/>
+    </row>
+    <row r="35" ht="27.75" customHeight="1" s="23">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>LHMI Path / Function Block</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>Measured Value</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="23">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>IA — Phase A Current (W1)</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Measurements → [SMAI/CT function] → IA</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="34" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="E36" s="29" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="23">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>IB — Phase B Current (W1)</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>Measurements → [SMAI/CT function] → IB</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="34" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="E37" s="29" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="23">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>IC — Phase C Current (W1)</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>Measurements → [SMAI/CT function] → IC</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="34" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="E38" s="29" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="23">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>IA — Phase A Current (W2 / Y-side)</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>Measurements → [SMAI W2] → IA (if 2nd CT set)</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr"/>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="34" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="E39" s="29" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="23">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>IB — Phase B Current (W2 / Y-side)</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="10" t="inlineStr"/>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="B40" s="33" t="n"/>
+      <c r="C40" s="35" t="n"/>
+      <c r="D40" s="34" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="E40" s="29" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="23">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>IC — Phase C Current (W2 / Y-side)</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="10" t="inlineStr"/>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="B41" s="33" t="n"/>
+      <c r="C41" s="35" t="n"/>
+      <c r="D41" s="34" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="E41" s="29" t="n"/>
+    </row>
+    <row r="42" ht="20.85" customHeight="1" s="23">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>VA — Phase A Voltage</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>Measurements → [voltage function] → VA
 (if VT fitted)</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr"/>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="C42" s="35" t="n"/>
+      <c r="D42" s="34" t="inlineStr">
         <is>
           <t>kV primary</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="E42" s="29" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="23">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>VB — Phase B Voltage</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>(if VT fitted)</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="C43" s="35" t="n"/>
+      <c r="D43" s="34" t="inlineStr">
         <is>
           <t>kV primary</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="E43" s="29" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="23">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>VC — Phase C Voltage</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>(if VT fitted)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr"/>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="C44" s="35" t="n"/>
+      <c r="D44" s="34" t="inlineStr">
         <is>
           <t>kV primary</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="E44" s="29" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="23">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>Measurements → [voltage function] → frequency</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr"/>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="C45" s="35" t="n"/>
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>Hz</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="E45" s="29" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="23">
+      <c r="A46" s="32" t="n"/>
+      <c r="B46" s="33" t="n"/>
+      <c r="C46" s="35" t="n"/>
+      <c r="D46" s="34" t="n"/>
+      <c r="E46" s="29" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="23">
+      <c r="A47" s="32" t="n"/>
+      <c r="B47" s="33" t="n"/>
+      <c r="C47" s="35" t="n"/>
+      <c r="D47" s="34" t="n"/>
+      <c r="E47" s="29" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="23">
+      <c r="A48" s="32" t="n"/>
+      <c r="B48" s="33" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="34" t="n"/>
+      <c r="E48" s="29" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="23">
+      <c r="A49" s="32" t="n"/>
+      <c r="B49" s="33" t="n"/>
+      <c r="C49" s="35" t="n"/>
+      <c r="D49" s="34" t="n"/>
+      <c r="E49" s="29" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="23">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>5.  CLOCK AND TIME SYNCHRONISATION</t>
         </is>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="18" t="n"/>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="26" t="n"/>
+      <c r="E51" s="27" t="n"/>
+    </row>
+    <row r="52" ht="27.75" customHeight="1" s="23">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>LHMI Path</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C52" s="31" t="inlineStr">
         <is>
           <t>IED Value</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D52" s="31" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
         <is>
           <t>Difference / OK?</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="53" ht="20.85" customHeight="1" s="23">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t>IED Date and Time</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Main menu → Diagnostics → IED status → Time
 (or Configuration → Time)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Today's date / current time</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="C53" s="29" t="n"/>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>Today's date / time</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="23">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>Time source (IRIG-B / IEEE 1588 / NTP)</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Main menu → Diagnostics → IED status → Time source</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>IRIG-B or IEEE 1588 preferred</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>IRIG-B or IEEE 1588</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="23">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>TIMESYNCHERROR = NORMAL</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B55" s="33" t="inlineStr">
         <is>
           <t>Main menu → Diagnostics → IED status → Signals</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="C55" s="29" t="n"/>
+      <c r="D55" s="34" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="E55" s="29" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="23">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t>Time difference (accept ≤ 1 s with sync; ≤ 10 s internal)</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>Compare LHMI time to GPS/phone reference</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="34" t="inlineStr">
         <is>
           <t>≤ 1 s</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="E56" s="29" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1" s="23">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>6.  RECENT EVENTS  (record most recent disturbance records / events)</t>
         </is>
       </c>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="18" t="n"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="B58" s="26" t="n"/>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="26" t="n"/>
+      <c r="E58" s="27" t="n"/>
+    </row>
+    <row r="59" ht="31.5" customHeight="1" s="23">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Events → Disturbance records list (most recent first).  PCM600: Event viewer shows all logged events with timestamps.  Record the most recent events; flag any unexplained trips or alarms.</t>
         </is>
       </c>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="17" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="18" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="B59" s="26" t="n"/>
+      <c r="C59" s="26" t="n"/>
+      <c r="D59" s="26" t="n"/>
+      <c r="E59" s="27" t="n"/>
+    </row>
+    <row r="60" ht="27.75" customHeight="1" s="23">
+      <c r="A60" s="31" t="inlineStr">
         <is>
           <t>Event #
 (most recent = 1)</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C60" s="31" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D60" s="31" t="inlineStr">
         <is>
           <t>Event Description / Type</t>
         </is>
       </c>
-      <c r="E56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="n">
+      <c r="E60" s="27" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="23">
+      <c r="A61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
+      <c r="B61" s="29" t="n"/>
+      <c r="C61" s="29" t="n"/>
+      <c r="D61" s="29" t="n"/>
+      <c r="E61" s="27" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="23">
+      <c r="A62" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="n">
+      <c r="B62" s="38" t="n"/>
+      <c r="C62" s="38" t="n"/>
+      <c r="D62" s="38" t="n"/>
+      <c r="E62" s="27" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="23">
+      <c r="A63" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="29" t="n"/>
+      <c r="D63" s="29" t="n"/>
+      <c r="E63" s="27" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="23">
+      <c r="A64" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B60" s="13" t="n"/>
-      <c r="C60" s="13" t="n"/>
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="18" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="n">
+      <c r="B64" s="38" t="n"/>
+      <c r="C64" s="38" t="n"/>
+      <c r="D64" s="38" t="n"/>
+      <c r="E64" s="27" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="23">
+      <c r="A65" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
+      <c r="B65" s="29" t="n"/>
+      <c r="C65" s="29" t="n"/>
+      <c r="D65" s="29" t="n"/>
+      <c r="E65" s="27" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="23">
+      <c r="A66" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="n">
+      <c r="B66" s="38" t="n"/>
+      <c r="C66" s="38" t="n"/>
+      <c r="D66" s="38" t="n"/>
+      <c r="E66" s="27" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="23">
+      <c r="A67" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="18" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n">
+      <c r="B67" s="29" t="n"/>
+      <c r="C67" s="29" t="n"/>
+      <c r="D67" s="29" t="n"/>
+      <c r="E67" s="27" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="23">
+      <c r="A68" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="n">
+      <c r="B68" s="38" t="n"/>
+      <c r="C68" s="38" t="n"/>
+      <c r="D68" s="38" t="n"/>
+      <c r="E68" s="27" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="23">
+      <c r="A69" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n">
+      <c r="B69" s="29" t="n"/>
+      <c r="C69" s="29" t="n"/>
+      <c r="D69" s="29" t="n"/>
+      <c r="E69" s="27" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="23">
+      <c r="A70" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="13" t="n"/>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="n"/>
-      <c r="E66" s="18" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="n">
+      <c r="B70" s="38" t="n"/>
+      <c r="C70" s="38" t="n"/>
+      <c r="D70" s="38" t="n"/>
+      <c r="E70" s="27" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="23">
+      <c r="A71" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="n">
+      <c r="B71" s="29" t="n"/>
+      <c r="C71" s="29" t="n"/>
+      <c r="D71" s="29" t="n"/>
+      <c r="E71" s="27" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="23">
+      <c r="A72" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="B68" s="13" t="n"/>
-      <c r="C68" s="13" t="n"/>
-      <c r="D68" s="13" t="n"/>
-      <c r="E68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Total disturbance records stored (as displayed on LHMI)</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="17" t="n"/>
-      <c r="D69" s="17" t="n"/>
-      <c r="E69" s="18" t="n"/>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="B72" s="38" t="n"/>
+      <c r="C72" s="38" t="n"/>
+      <c r="D72" s="38" t="n"/>
+      <c r="E72" s="27" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="23">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>Total disturbance records (as displayed on LHMI)</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="27" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1" s="23">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>7.  DCS / ABB 800XA COMMUNICATION CHECK</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="17" t="n"/>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="18" t="n"/>
-    </row>
-    <row r="72" ht="36" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="B75" s="26" t="n"/>
+      <c r="C75" s="26" t="n"/>
+      <c r="D75" s="26" t="n"/>
+      <c r="E75" s="27" t="n"/>
+    </row>
+    <row r="76" ht="36" customHeight="1" s="23">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Open the IED faceplate in the ABB 800XA control system. Verify live values (currents, IED status indicators) are updating. The 800XA communicates via IEC 61850 GOOSE / MMS. No yellow or red communication alarm objects should be present.</t>
         </is>
       </c>
-      <c r="B72" s="17" t="n"/>
-      <c r="C72" s="17" t="n"/>
-      <c r="D72" s="17" t="n"/>
-      <c r="E72" s="18" t="n"/>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="B76" s="26" t="n"/>
+      <c r="C76" s="26" t="n"/>
+      <c r="D76" s="26" t="n"/>
+      <c r="E76" s="27" t="n"/>
+    </row>
+    <row r="77" ht="27.75" customHeight="1" s="23">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B77" s="31" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C77" s="31" t="inlineStr">
         <is>
           <t>Result
 (Y / N)</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D77" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="E77" s="27" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="23">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>800XA faceplate opened</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B78" s="34" t="inlineStr">
         <is>
           <t>Navigate to IED faceplate in 800XA Plant Explorer</t>
         </is>
       </c>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="18" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="C78" s="35" t="n"/>
+      <c r="D78" s="29" t="n"/>
+      <c r="E78" s="27" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="23">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>IED Status = HEALTHY / OK</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B79" s="34" t="inlineStr">
         <is>
           <t>Green status indicator on faceplate — not alarm/fault colour</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="C79" s="35" t="n"/>
+      <c r="D79" s="29" t="n"/>
+      <c r="E79" s="27" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="23">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>Live current values updating</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>Measured currents on faceplate match LHMI readings (not frozen)</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="B80" s="34" t="inlineStr">
+        <is>
+          <t>Measured currents on faceplate match LHMI readings</t>
+        </is>
+      </c>
+      <c r="C80" s="35" t="n"/>
+      <c r="D80" s="29" t="n"/>
+      <c r="E80" s="27" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="23">
+      <c r="A81" s="28" t="inlineStr">
         <is>
           <t>No communication alarm</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B81" s="34" t="inlineStr">
         <is>
           <t>No yellow/red GOOSE or MMS communication alarm objects</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="18" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="C81" s="35" t="n"/>
+      <c r="D81" s="29" t="n"/>
+      <c r="E81" s="27" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="23">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>800XA object path (record below)</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B82" s="34" t="inlineStr">
         <is>
           <t>e.g. 'Site / Substation / Relay Tag / Faceplate'</t>
         </is>
       </c>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="18" t="n"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="C82" s="35" t="n"/>
+      <c r="D82" s="29" t="n"/>
+      <c r="E82" s="27" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1" s="23">
+      <c r="A84" s="25" t="inlineStr">
         <is>
           <t>8.  OPTIONAL — CLEAR EVENT BUFFERS  (only if required by your procedure)</t>
         </is>
       </c>
-      <c r="B80" s="17" t="n"/>
-      <c r="C80" s="17" t="n"/>
-      <c r="D80" s="17" t="n"/>
-      <c r="E80" s="18" t="n"/>
-    </row>
-    <row r="81" ht="36" customHeight="1">
-      <c r="A81" s="14" t="inlineStr">
+      <c r="B84" s="26" t="n"/>
+      <c r="C84" s="26" t="n"/>
+      <c r="D84" s="26" t="n"/>
+      <c r="E84" s="27" t="n"/>
+    </row>
+    <row r="85" ht="36" customHeight="1" s="23">
+      <c r="A85" s="40" t="inlineStr">
         <is>
           <t>Only clear events if required by site procedure. Ensure all events have been downloaded/recorded BEFORE clearing. LHMI: Main menu → Events → [select event] → Clear  (or Clear all).  Internal events (INTERRSIG log) clear automatically after 40 events (FIFO).</t>
         </is>
       </c>
-      <c r="B81" s="17" t="n"/>
-      <c r="C81" s="17" t="n"/>
-      <c r="D81" s="17" t="n"/>
-      <c r="E81" s="18" t="n"/>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="B85" s="26" t="n"/>
+      <c r="C85" s="26" t="n"/>
+      <c r="D85" s="26" t="n"/>
+      <c r="E85" s="27" t="n"/>
+    </row>
+    <row r="86" ht="27.75" customHeight="1" s="23">
+      <c r="A86" s="31" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B86" s="31" t="inlineStr">
         <is>
           <t>LHMI Path</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C86" s="31" t="inlineStr">
         <is>
           <t>Performed?
 (Y / N / N/A)</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D86" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E82" s="18" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="E86" s="27" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="23">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>Download disturbance records</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B87" s="34" t="inlineStr">
         <is>
           <t>PCM600 → Disturbance handling → Save to file</t>
         </is>
       </c>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="C87" s="35" t="n"/>
+      <c r="D87" s="29" t="n"/>
+      <c r="E87" s="27" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="23">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>Clear disturbance records</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B88" s="34" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Events → Clear disturbance records</t>
         </is>
       </c>
-      <c r="C84" s="10" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="18" t="n"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="C88" s="35" t="n"/>
+      <c r="D88" s="29" t="n"/>
+      <c r="E88" s="27" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1" s="23">
+      <c r="A90" s="25" t="inlineStr">
         <is>
           <t>9.  OBSERVATIONS AND CORRECTIVE ACTIONS</t>
         </is>
       </c>
-      <c r="B86" s="17" t="n"/>
-      <c r="C86" s="17" t="n"/>
-      <c r="D86" s="17" t="n"/>
-      <c r="E86" s="18" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="15" t="n"/>
-      <c r="B87" s="19" t="n"/>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="19" t="n"/>
-      <c r="E87" s="20" t="n"/>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="21" t="n"/>
-      <c r="E88" s="22" t="n"/>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="21" t="n"/>
-      <c r="E89" s="22" t="n"/>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="23" t="n"/>
-      <c r="B90" s="24" t="n"/>
-      <c r="C90" s="24" t="n"/>
-      <c r="D90" s="24" t="n"/>
-      <c r="E90" s="25" t="n"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="B90" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="27" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="23">
+      <c r="A91" s="41" t="n"/>
+      <c r="B91" s="42" t="n"/>
+      <c r="C91" s="42" t="n"/>
+      <c r="D91" s="42" t="n"/>
+      <c r="E91" s="43" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1" s="23">
+      <c r="A92" s="44" t="n"/>
+      <c r="E92" s="45" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1" s="23">
+      <c r="A93" s="44" t="n"/>
+      <c r="E93" s="45" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1" s="23">
+      <c r="A94" s="46" t="n"/>
+      <c r="B94" s="47" t="n"/>
+      <c r="C94" s="47" t="n"/>
+      <c r="D94" s="47" t="n"/>
+      <c r="E94" s="48" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1" s="23">
+      <c r="A96" s="25" t="inlineStr">
         <is>
           <t>10.  SIGN-OFF</t>
         </is>
       </c>
-      <c r="B92" s="17" t="n"/>
-      <c r="C92" s="17" t="n"/>
-      <c r="D92" s="17" t="n"/>
-      <c r="E92" s="18" t="n"/>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="B96" s="26" t="n"/>
+      <c r="C96" s="26" t="n"/>
+      <c r="D96" s="26" t="n"/>
+      <c r="E96" s="27" t="n"/>
+    </row>
+    <row r="97" ht="27.75" customHeight="1" s="23">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B97" s="31" t="inlineStr">
         <is>
           <t>Name (print)</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C97" s="31" t="inlineStr">
         <is>
           <t>Signature</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D97" s="31" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E93" s="18" t="n"/>
-    </row>
-    <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="E97" s="27" t="n"/>
+    </row>
+    <row r="98" ht="24" customHeight="1" s="23">
+      <c r="A98" s="28" t="inlineStr">
         <is>
           <t>Technician</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n"/>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="18" t="n"/>
-    </row>
-    <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="B98" s="29" t="n"/>
+      <c r="C98" s="29" t="n"/>
+      <c r="D98" s="29" t="n"/>
+      <c r="E98" s="27" t="n"/>
+    </row>
+    <row r="99" ht="24" customHeight="1" s="23">
+      <c r="A99" s="28" t="inlineStr">
         <is>
           <t>Supervisor / Witness</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="18" t="n"/>
-    </row>
+      <c r="B99" s="29" t="n"/>
+      <c r="C99" s="29" t="n"/>
+      <c r="D99" s="29" t="n"/>
+      <c r="E99" s="27" t="n"/>
+    </row>
+    <row r="1048576" ht="12.8" customHeight="1" s="23"/>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="D69:E69"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="D60:E60"/>
-    <mergeCell ref="B9:E9"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="D63:E63"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D99:E99"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="D84:E84"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="D80:E80"/>
     <mergeCell ref="D65:E65"/>
+    <mergeCell ref="B10:E10"/>
     <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D95:E95"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="A91:E94"/>
+    <mergeCell ref="A90:E90"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="D61:E61"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D97:E97"/>
     <mergeCell ref="D66:E66"/>
-    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="D75:E75"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D72:E72"/>
     <mergeCell ref="D78:E78"/>
-    <mergeCell ref="A86:E86"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D62:E62"/>
-    <mergeCell ref="D93:E93"/>
     <mergeCell ref="A14:E14"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D71:E71"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="D68:E68"/>
-    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="D64:E64"/>
-    <mergeCell ref="A72:E72"/>
     <mergeCell ref="D82:E82"/>
-    <mergeCell ref="A87:E90"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="D98:E98"/>
     <mergeCell ref="D67:E67"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="D73:E73"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="D79:E79"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.511811023622047" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Bold"&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</evenFooter>
     <firstHeader/>
@@ -1971,1115 +2039,1114 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E88"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" style="22" min="1" max="1"/>
+    <col width="34" customWidth="1" style="22" min="2" max="2"/>
+    <col width="14" customWidth="1" style="22" min="3" max="3"/>
+    <col width="12" customWidth="1" style="22" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="27.75" customHeight="1" s="23">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>ABB RELION 615 IED — BIENNIAL (2-YEARLY) VISUAL CHECK SHEET  (REF615 / RET615 / REM615 / REU615)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="23">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>1.  IED AND SITE INFORMATION</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="17" t="n"/>
-      <c r="E3" s="18" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="27" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="23">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>IED Model</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>REF615  /  RET615  /  REM615  /  REU615  (circle one)</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="18" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="27" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="23">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Protected Equipment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="18" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="27" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="23">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Site / Substation</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="18" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="27" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="23">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>IED Name</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="18" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="27" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="23">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Panel / Cubicle Tag</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="27" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="23">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Work Order No.</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="18" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="23">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Date of Check</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="18" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="27" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="23">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Technician Name</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="18" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="27" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="23">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Next Check Due</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>(2 years from date above)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="18" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="27" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="23">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>2.  CONNECTION METHOD</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="27" t="n"/>
+    </row>
+    <row r="15" ht="63.75" customHeight="1" s="23">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>OPTION A — LHMI only: The 615 series has a basic text-display LHMI (4 lines). Use the push-buttons (← → ↑ ↓ and Enter/C) to navigate menus. Main menu appears on pressing the MENU/HOME button.
 OPTION B — Ethernet + PCM600 laptop: Connect Ethernet to the front RJ45 port (if available on your model). Open PCM600 → Online monitoring for live values. Default IP is on the IED nameplate or in LHMI: Main menu → Configuration → Communication → Ethernet.
 OPTION C — Ethernet + web browser: Newer 615 C/D models support a built-in web server — navigate to IED IP address in a browser.</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="18" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="27" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="23">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Connection method used today</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>LHMI only  /  Ethernet + PCM600  /  Ethernet + browser  (delete as applicable)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="18" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="27" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="23">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>3.  SELF-TEST AND IED STATUS</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="18" t="n"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="27" t="n"/>
+    </row>
+    <row r="19" ht="39.75" customHeight="1" s="23">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>Key LED indicators on front panel:  READY (green, solid) = IED healthy and in service.  START (yellow) = protection element picked up (may be normal under load).  TRIP (red) = protection has tripped.  Self-supervision: LHMI: Main menu → Monitoring → Self-supervision → IED status.</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="27" t="n"/>
+    </row>
+    <row r="20" ht="27.75" customHeight="1" s="23">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Check Item</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>How to Read / Where to Look</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="28.35" customHeight="1" s="23">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>READY LED (green, solid)</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="50" t="inlineStr">
         <is>
           <t>Visual — front panel. Solid green = IED healthy</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>Solid green ON</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="29" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="23">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>No unexpected TRIP LED (red)</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="50" t="inlineStr">
         <is>
           <t>Visual — front panel red LED</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
         <is>
           <t>Off (or explained by recent fault)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="29" t="n"/>
+    </row>
+    <row r="23" ht="28.35" customHeight="1" s="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>No alarm indication on LHMI display</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="50" t="inlineStr">
         <is>
           <t>Text display — check for error or alarm message on home screen</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="51" t="inlineStr">
         <is>
           <t>No error messages</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="28.35" customHeight="1" s="23">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>IED self-supervision — IED status</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="50" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Monitoring → Self-supervision → IED status</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="51" t="inlineStr">
         <is>
           <t>HEALTHY / OK</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="29" t="n"/>
+    </row>
+    <row r="25" ht="28.35" customHeight="1" s="23">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Internal fault indicator</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="50" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Monitoring → Self-supervision → Internal fault</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="51" t="inlineStr">
         <is>
           <t>No internal faults</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="28.35" customHeight="1" s="23">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>Power supply OK</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="50" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Monitoring → Self-supervision</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="51" t="inlineStr">
         <is>
           <t>PSU OK</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="29" t="n"/>
+    </row>
+    <row r="27" ht="28.35" customHeight="1" s="23">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>Communication module (if IEC 61850 fitted)</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="50" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Monitoring → Self-supervision → IEC 61850</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="51" t="inlineStr">
         <is>
           <t>OK / No error</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="4" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="29" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="23">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>4.  ANALOGUE MEASUREMENTS  (Primary Values)</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="27" t="n"/>
+    </row>
+    <row r="30" ht="39.75" customHeight="1" s="23">
+      <c r="A30" s="49" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Monitoring → Measurements → Current (or Voltage).  All values shown in primary units. PCM600 Signal Monitor also displays live primary values.  Record current values. Flag anything obviously abnormal (e.g. one phase zero while others are loaded).</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="27" t="n"/>
+    </row>
+    <row r="31" ht="27.75" customHeight="1" s="23">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>LHMI Path</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>Measured Value</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="32" ht="28.35" customHeight="1" s="23">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>IL1 — Phase L1 Current (primary)</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr">
         <is>
           <t>Monitoring → Measurements → Current → IL1</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="51" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="E32" s="29" t="n"/>
+    </row>
+    <row r="33" ht="28.35" customHeight="1" s="23">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>IL2 — Phase L2 Current (primary)</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="50" t="inlineStr">
         <is>
           <t>Monitoring → Measurements → Current → IL2</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="51" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="E33" s="29" t="n"/>
+    </row>
+    <row r="34" ht="28.35" customHeight="1" s="23">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>IL3 — Phase L3 Current (primary)</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="50" t="inlineStr">
         <is>
           <t>Monitoring → Measurements → Current → IL3</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="51" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="E34" s="29" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="23">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>I0 / IN — Residual Current</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="50" t="inlineStr">
         <is>
           <t>Monitoring → Measurements → Current → I0</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="51" t="inlineStr">
         <is>
           <t>A primary</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="E35" s="29" t="n"/>
+    </row>
+    <row r="36" ht="41.75" customHeight="1" s="23">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>UL1 — Phase Voltage (primary)</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="50" t="inlineStr">
         <is>
           <t>Monitoring → Measurements → Voltage → UL1
 (if VT fitted)</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="51" t="inlineStr">
         <is>
           <t>kV primary</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="E36" s="29" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="23">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>UL2 — Phase Voltage (primary)</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="50" t="inlineStr">
         <is>
           <t>(if VT fitted)</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="51" t="inlineStr">
         <is>
           <t>kV primary</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="E37" s="29" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="23">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>UL3 — Phase Voltage (primary)</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="50" t="inlineStr">
         <is>
           <t>(if VT fitted)</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="51" t="inlineStr">
         <is>
           <t>kV primary</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="E38" s="29" t="n"/>
+    </row>
+    <row r="39" ht="28.35" customHeight="1" s="23">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="50" t="inlineStr">
         <is>
           <t>Monitoring → Measurements → Frequency
 (if VT fitted)</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="51" t="inlineStr">
         <is>
           <t>Hz</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="E39" s="29" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="23">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>5.  CLOCK AND TIME SYNCHRONISATION</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="18" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+      <c r="E41" s="27" t="n"/>
+    </row>
+    <row r="42" ht="27.75" customHeight="1" s="23">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="31" t="inlineStr">
         <is>
           <t>LHMI Path</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="31" t="inlineStr">
         <is>
           <t>IED Value</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="31" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="31" t="inlineStr">
         <is>
           <t>Difference / OK?</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="43" ht="41.75" customHeight="1" s="23">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>IED Date and Time</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="50" t="inlineStr">
         <is>
           <t>LHMI: Main menu → General settings → Date and time
 (or shown on LHMI home screen)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="51" t="inlineStr">
         <is>
           <t>Today's date / current time</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="E43" s="29" t="n"/>
+    </row>
+    <row r="44" ht="28.35" customHeight="1" s="23">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>Time source (IRIG-B / SNTP / Internal)</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="50" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Configuration → Time synchronisation</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="51" t="inlineStr">
         <is>
           <t>IRIG-B or SNTP preferred</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="E44" s="29" t="n"/>
+    </row>
+    <row r="45" ht="28.35" customHeight="1" s="23">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>Time difference (accept ≤ 10 s)</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="50" t="inlineStr">
         <is>
           <t>Compare LHMI time to GPS / phone reference</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="C45" s="29" t="n"/>
+      <c r="D45" s="51" t="inlineStr">
         <is>
           <t>≤ 10 s</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="E45" s="29" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="23">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>6.  RECENT EVENTS  (record most recent events from the event list)</t>
         </is>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="18" t="n"/>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="B47" s="26" t="n"/>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="27" t="n"/>
+    </row>
+    <row r="48" ht="27.75" customHeight="1" s="23">
+      <c r="A48" s="49" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Events → Event list (most recent first).  PCM600: Event viewer.  Record the most recent events. Flag any unexplained TRIP or FAULT events.</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="18" t="n"/>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="B48" s="26" t="n"/>
+      <c r="C48" s="26" t="n"/>
+      <c r="D48" s="26" t="n"/>
+      <c r="E48" s="27" t="n"/>
+    </row>
+    <row r="49" ht="27.75" customHeight="1" s="23">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>Event #
 (most recent = 1)</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="31" t="inlineStr">
         <is>
           <t>Event Description / Type</t>
         </is>
       </c>
-      <c r="E49" s="18" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="n">
+      <c r="E49" s="27" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="23">
+      <c r="A50" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="18" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="29" t="n"/>
+      <c r="E50" s="27" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="23">
+      <c r="A51" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="18" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="n">
+      <c r="B51" s="38" t="n"/>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="38" t="n"/>
+      <c r="E51" s="27" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="23">
+      <c r="A52" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="18" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="B52" s="29" t="n"/>
+      <c r="C52" s="29" t="n"/>
+      <c r="D52" s="29" t="n"/>
+      <c r="E52" s="27" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="23">
+      <c r="A53" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="18" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="n">
+      <c r="B53" s="38" t="n"/>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="38" t="n"/>
+      <c r="E53" s="27" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="23">
+      <c r="A54" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="18" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="B54" s="29" t="n"/>
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="29" t="n"/>
+      <c r="E54" s="27" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="23">
+      <c r="A55" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="18" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="n">
+      <c r="B55" s="38" t="n"/>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="38" t="n"/>
+      <c r="E55" s="27" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="23">
+      <c r="A56" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="n">
+      <c r="B56" s="29" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="29" t="n"/>
+      <c r="E56" s="27" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="23">
+      <c r="A57" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B57" s="13" t="n"/>
-      <c r="C57" s="13" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="n">
+      <c r="B57" s="38" t="n"/>
+      <c r="C57" s="38" t="n"/>
+      <c r="D57" s="38" t="n"/>
+      <c r="E57" s="27" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="23">
+      <c r="A58" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="n">
+      <c r="B58" s="29" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="27" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="23">
+      <c r="A59" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="13" t="n"/>
-      <c r="C59" s="13" t="n"/>
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="n">
+      <c r="B59" s="38" t="n"/>
+      <c r="C59" s="38" t="n"/>
+      <c r="D59" s="38" t="n"/>
+      <c r="E59" s="27" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="23">
+      <c r="A60" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="18" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="n">
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="29" t="n"/>
+      <c r="E60" s="27" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="23">
+      <c r="A61" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="B61" s="13" t="n"/>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="B61" s="38" t="n"/>
+      <c r="C61" s="38" t="n"/>
+      <c r="D61" s="38" t="n"/>
+      <c r="E61" s="27" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="23">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>Total events in event list (as shown on LHMI)</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="17" t="n"/>
-      <c r="D62" s="17" t="n"/>
-      <c r="E62" s="18" t="n"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B62" s="29" t="n"/>
+      <c r="C62" s="26" t="n"/>
+      <c r="D62" s="26" t="n"/>
+      <c r="E62" s="27" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1" s="23">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>7.  DCS / ABB 800XA COMMUNICATION CHECK</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="17" t="n"/>
-      <c r="D64" s="17" t="n"/>
-      <c r="E64" s="18" t="n"/>
-    </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="B64" s="26" t="n"/>
+      <c r="C64" s="26" t="n"/>
+      <c r="D64" s="26" t="n"/>
+      <c r="E64" s="27" t="n"/>
+    </row>
+    <row r="65" ht="36" customHeight="1" s="23">
+      <c r="A65" s="49" t="inlineStr">
         <is>
           <t>Open the IED faceplate in the ABB 800XA control system. Verify live values and IED status are updating. The 615 series typically communicates via IEC 61850, DNP3.0, or Modbus.  No yellow or red communication alarm objects should be present on the 800XA faceplate.</t>
         </is>
       </c>
-      <c r="B65" s="17" t="n"/>
-      <c r="C65" s="17" t="n"/>
-      <c r="D65" s="17" t="n"/>
-      <c r="E65" s="18" t="n"/>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="B65" s="26" t="n"/>
+      <c r="C65" s="26" t="n"/>
+      <c r="D65" s="26" t="n"/>
+      <c r="E65" s="27" t="n"/>
+    </row>
+    <row r="66" ht="27.75" customHeight="1" s="23">
+      <c r="A66" s="31" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="31" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" s="31" t="inlineStr">
         <is>
           <t>Result
 (Y / N)</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E66" s="18" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="E66" s="27" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="23">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>800XA faceplate opened</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="51" t="inlineStr">
         <is>
           <t>Navigate to IED faceplate in 800XA Plant Explorer</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="C67" s="35" t="n"/>
+      <c r="D67" s="29" t="n"/>
+      <c r="E67" s="27" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="23">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>IED Status = HEALTHY / OK on faceplate</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="51" t="inlineStr">
         <is>
           <t>Green status indicator — not alarm/fault colour</t>
         </is>
       </c>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="C68" s="35" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="27" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="23">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Live current values updating</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="51" t="inlineStr">
         <is>
           <t>Measured currents on faceplate match LHMI readings (not frozen or zero under load)</t>
         </is>
       </c>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="C69" s="35" t="n"/>
+      <c r="D69" s="29" t="n"/>
+      <c r="E69" s="27" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="23">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>No communication alarm</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="51" t="inlineStr">
         <is>
           <t>No yellow/red comms alarm objects on faceplate</t>
         </is>
       </c>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="18" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="C70" s="35" t="n"/>
+      <c r="D70" s="29" t="n"/>
+      <c r="E70" s="27" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="23">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>800XA object path (record below)</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="51" t="inlineStr">
         <is>
           <t>e.g. 'Site / Substation / Relay Tag / Faceplate'</t>
         </is>
       </c>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="18" t="n"/>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="C71" s="35" t="n"/>
+      <c r="D71" s="29" t="n"/>
+      <c r="E71" s="27" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1" s="23">
+      <c r="A73" s="25" t="inlineStr">
         <is>
           <t>8.  OPTIONAL — CLEAR EVENTS  (only if required by your procedure)</t>
         </is>
       </c>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="17" t="n"/>
-      <c r="E73" s="18" t="n"/>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="14" t="inlineStr">
+      <c r="B73" s="26" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="27" t="n"/>
+    </row>
+    <row r="74" ht="27.75" customHeight="1" s="23">
+      <c r="A74" s="52" t="inlineStr">
         <is>
           <t>Only clear events if required by site procedure. Download/record all events BEFORE clearing. LHMI: Main menu → Events → Event list → Clear all (or select individual events).</t>
         </is>
       </c>
-      <c r="B74" s="17" t="n"/>
-      <c r="C74" s="17" t="n"/>
-      <c r="D74" s="17" t="n"/>
-      <c r="E74" s="18" t="n"/>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="B74" s="26" t="n"/>
+      <c r="C74" s="26" t="n"/>
+      <c r="D74" s="26" t="n"/>
+      <c r="E74" s="27" t="n"/>
+    </row>
+    <row r="75" ht="27.75" customHeight="1" s="23">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="31" t="inlineStr">
         <is>
           <t>LHMI Path</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" s="31" t="inlineStr">
         <is>
           <t>Performed?
 (Y / N / N/A)</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" s="31" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="E75" s="27" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="23">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Download event list</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B76" s="51" t="inlineStr">
         <is>
           <t>PCM600 → Event viewer → Export / Save</t>
         </is>
       </c>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="C76" s="35" t="n"/>
+      <c r="D76" s="29" t="n"/>
+      <c r="E76" s="27" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="23">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Clear event list</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B77" s="51" t="inlineStr">
         <is>
           <t>LHMI: Main menu → Events → Event list → Clear all</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="18" t="n"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="C77" s="35" t="n"/>
+      <c r="D77" s="29" t="n"/>
+      <c r="E77" s="27" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1" s="23">
+      <c r="A79" s="25" t="inlineStr">
         <is>
           <t>9.  OBSERVATIONS AND CORRECTIVE ACTIONS</t>
         </is>
       </c>
-      <c r="B79" s="17" t="n"/>
-      <c r="C79" s="17" t="n"/>
-      <c r="D79" s="17" t="n"/>
-      <c r="E79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="15" t="n"/>
-      <c r="B80" s="19" t="n"/>
-      <c r="C80" s="19" t="n"/>
-      <c r="D80" s="19" t="n"/>
-      <c r="E80" s="20" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="21" t="n"/>
-      <c r="E81" s="22" t="n"/>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="21" t="n"/>
-      <c r="E82" s="22" t="n"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="23" t="n"/>
-      <c r="B83" s="24" t="n"/>
-      <c r="C83" s="24" t="n"/>
-      <c r="D83" s="24" t="n"/>
-      <c r="E83" s="25" t="n"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="B79" s="26" t="n"/>
+      <c r="C79" s="26" t="n"/>
+      <c r="D79" s="26" t="n"/>
+      <c r="E79" s="27" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="23">
+      <c r="A80" s="41" t="n"/>
+      <c r="B80" s="42" t="n"/>
+      <c r="C80" s="42" t="n"/>
+      <c r="D80" s="42" t="n"/>
+      <c r="E80" s="43" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1" s="23">
+      <c r="A81" s="44" t="n"/>
+      <c r="E81" s="45" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1" s="23">
+      <c r="A82" s="44" t="n"/>
+      <c r="E82" s="45" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1" s="23">
+      <c r="A83" s="46" t="n"/>
+      <c r="B83" s="47" t="n"/>
+      <c r="C83" s="47" t="n"/>
+      <c r="D83" s="47" t="n"/>
+      <c r="E83" s="48" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1" s="23">
+      <c r="A85" s="25" t="inlineStr">
         <is>
           <t>10.  SIGN-OFF</t>
         </is>
       </c>
-      <c r="B85" s="17" t="n"/>
-      <c r="C85" s="17" t="n"/>
-      <c r="D85" s="17" t="n"/>
-      <c r="E85" s="18" t="n"/>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="B85" s="26" t="n"/>
+      <c r="C85" s="26" t="n"/>
+      <c r="D85" s="26" t="n"/>
+      <c r="E85" s="27" t="n"/>
+    </row>
+    <row r="86" ht="27.75" customHeight="1" s="23">
+      <c r="A86" s="31" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="31" t="inlineStr">
         <is>
           <t>Name (print)</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="31" t="inlineStr">
         <is>
           <t>Signature</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="31" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E86" s="18" t="n"/>
-    </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="E86" s="27" t="n"/>
+    </row>
+    <row r="87" ht="24" customHeight="1" s="23">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>Technician</t>
         </is>
       </c>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="18" t="n"/>
-    </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="B87" s="29" t="n"/>
+      <c r="C87" s="29" t="n"/>
+      <c r="D87" s="29" t="n"/>
+      <c r="E87" s="27" t="n"/>
+    </row>
+    <row r="88" ht="24" customHeight="1" s="23">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>Supervisor / Witness</t>
         </is>
       </c>
-      <c r="B88" s="4" t="n"/>
-      <c r="C88" s="4" t="n"/>
-      <c r="D88" s="4" t="n"/>
-      <c r="E88" s="18" t="n"/>
+      <c r="B88" s="29" t="n"/>
+      <c r="C88" s="29" t="n"/>
+      <c r="D88" s="29" t="n"/>
+      <c r="E88" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="54">
@@ -3095,6 +3162,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A80:E83"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="A79:E79"/>
     <mergeCell ref="D77:E77"/>
     <mergeCell ref="D52:E52"/>
@@ -3130,19 +3198,19 @@
     <mergeCell ref="D55:E55"/>
     <mergeCell ref="D68:E68"/>
     <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D88:E88"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D88:E88"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="D59:E59"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.511811023622047" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Bold"&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter>&amp;L&amp;8 &amp;K1F4E79&amp;BContact Energy&amp;C&amp;8 ABB Biennial Visual Check&amp;R&amp;8 Page &amp;P of &amp;N</evenFooter>
     <firstHeader/>
